--- a/scikitlearn/iris_train.xlsx
+++ b/scikitlearn/iris_train.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alsonbasnet/Desktop/ipynp/scikitlearn/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E59975DE-B493-034F-96CC-A52DFE17C2B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51D27A51-8B21-8242-ADF0-9E89D9B9F928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="20180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$151</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$32</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
